--- a/artfynd/S 2739-2022 artfynd.xlsx
+++ b/artfynd/S 2739-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3498,57 +3498,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>82697054</v>
+        <v>137255053</v>
       </c>
       <c r="B25" t="n">
-        <v>5317</v>
+        <v>9418</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>101312</v>
+        <v>101246</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Molnfläcksbock</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Mesosa nebulosa</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fabricius, 1781)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Enerum löväng, Öl</t>
+          <t>Grytmon, Öl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620257</v>
+        <v>619642</v>
       </c>
       <c r="R25" t="n">
-        <v>6352583</v>
+        <v>6352327</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3572,17 +3572,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-03-08</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>21:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-03-08</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>21:42</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Talrik</t>
+          <t>Levande hane</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3591,105 +3601,80 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Olof Persson</t>
+          <t>Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Olof Persson, Pav Johnsson, Michael Tholin, Emil Persson, Jesper Hansson, Pontus Axén, Robin Isaksson, Raul Vicente, Ola Hammarström</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Gemensamma artsatsningar</t>
-        </is>
-      </c>
+          <t>Via Torbjörn Blixt</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82697054</t>
+          <t>https://artportalen.se/Sighting/137255053</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>60698345</v>
+        <v>82697054</v>
       </c>
       <c r="B26" t="n">
-        <v>45347</v>
+        <v>5317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>101819</v>
+        <v>101312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skärrande gräshoppa</t>
+          <t>Molnfläcksbock</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Stauroderus scalaris</t>
+          <t>Mesosa nebulosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fischer-Waldheim, 1846)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1781)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>V Hunderum, Öl</t>
+          <t>Enerum löväng, Öl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>619712</v>
+        <v>620257</v>
       </c>
       <c r="R26" t="n">
-        <v>6352276</v>
+        <v>6352583</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3713,27 +3698,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2016-07-20</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:09</t>
+          <t>2020-03-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2016-07-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:09</t>
+          <t>2020-03-08</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ingen jättelämplig miljö med tanke på läget i skog.</t>
+          <t>Talrik</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3742,39 +3717,35 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Liten gräsbevuxen glänta i skog. Sand i dagen.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Oskar Kindvall</t>
+          <t>Olof Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Oskar Kindvall, Malin Strand</t>
+          <t>Olof Persson, Pav Johnsson, Michael Tholin, Emil Persson, Jesper Hansson, Pontus Axén, Robin Isaksson, Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>ÅGP Skärrande gräshoppa N Öland (Calluna_OKL0003)</t>
+          <t>Gemensamma artsatsningar</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60698345</t>
+          <t>https://artportalen.se/Sighting/82697054</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>60698347</v>
+        <v>60698345</v>
       </c>
       <c r="B27" t="n">
         <v>45347</v>
@@ -3804,7 +3775,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3817,7 +3788,11 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>spel</t>
@@ -3830,17 +3805,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hunderum, Öl</t>
+          <t>V Hunderum, Öl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>619781</v>
+        <v>619712</v>
       </c>
       <c r="R27" t="n">
-        <v>6352327</v>
+        <v>6352276</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3884,7 +3859,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Mycket hög täthet. Ny förekomst. En del av sandblottorna har tillkommit i samband med brasor som anlagts vid flera tillfällen på platsen.</t>
+          <t>Ingen jättelämplig miljö med tanke på läget i skog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3898,7 +3873,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Torräng med riklig blomning och flera ganska stora sandblottor.</t>
+          <t>Liten gräsbevuxen glänta i skog. Sand i dagen.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3919,58 +3894,76 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60698347</t>
+          <t>https://artportalen.se/Sighting/60698345</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>64721396</v>
+        <v>60698347</v>
       </c>
       <c r="B28" t="n">
-        <v>58112</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103020</v>
+        <v>101819</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Skärrande gräshoppa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Stauroderus scalaris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(Fischer-Waldheim, 1846)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>spel</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Enerums gamla bygata, Öl</t>
+          <t>Hunderum, Öl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620445</v>
+        <v>619781</v>
       </c>
       <c r="R28" t="n">
-        <v>6352579</v>
+        <v>6352327</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3997,12 +3990,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2016-07-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2016-07-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Mycket hög täthet. Ny förekomst. En del av sandblottorna har tillkommit i samband med brasor som anlagts vid flera tillfällen på platsen.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4013,71 +4021,82 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Torräng med riklig blomning och flera ganska stora sandblottor.</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Oskar Kindvall</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Tommy Knutsson, Mikael Jeppson, Annika Sohlman</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Oskar Kindvall, Malin Strand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>ÅGP Skärrande gräshoppa N Öland (Calluna_OKL0003)</t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64721396</t>
+          <t>https://artportalen.se/Sighting/60698347</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>82697033</v>
+        <v>64721396</v>
       </c>
       <c r="B29" t="n">
-        <v>30288</v>
+        <v>58112</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>200985</v>
+        <v>103020</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Enerum löväng, Öl</t>
+          <t>Enerums gamla bygata, Öl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620257</v>
+        <v>620445</v>
       </c>
       <c r="R29" t="n">
-        <v>6352583</v>
+        <v>6352579</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4104,12 +4123,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-03-08</t>
+          <t>2017-04-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-03-08</t>
+          <t>2017-04-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4118,38 +4137,33 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Olof Persson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Olof Persson, Pav Johnsson, Michael Tholin, Emil Persson, Jesper Hansson, Pontus Axén, Robin Isaksson, Raul Vicente, Ola Hammarström</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Gemensamma artsatsningar</t>
-        </is>
-      </c>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Tommy Knutsson, Mikael Jeppson, Annika Sohlman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82697033</t>
+          <t>https://artportalen.se/Sighting/64721396</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2210317</v>
+        <v>82697033</v>
       </c>
       <c r="B30" t="n">
-        <v>107608</v>
+        <v>30288</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4157,39 +4171,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219686</v>
+        <v>200985</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hunderum, Öl</t>
+          <t>Enerum löväng, Öl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620268</v>
+        <v>620257</v>
       </c>
       <c r="R30" t="n">
-        <v>6352509</v>
+        <v>6352583</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4216,12 +4230,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2012-04-21</t>
+          <t>2020-03-08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2012-04-21</t>
+          <t>2020-03-08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4230,39 +4244,35 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>nyröjd betesmark med löv/barrskog</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Olof Persson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Olof Persson, Pav Johnsson, Michael Tholin, Emil Persson, Jesper Hansson, Pontus Axén, Robin Isaksson, Raul Vicente, Ola Hammarström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Gemensamma artsatsningar</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2210317</t>
+          <t>https://artportalen.se/Sighting/82697033</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2210318</v>
+        <v>2210317</v>
       </c>
       <c r="B31" t="n">
         <v>107608</v>
@@ -4302,10 +4312,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620362</v>
+        <v>620268</v>
       </c>
       <c r="R31" t="n">
-        <v>6352577</v>
+        <v>6352509</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4372,33 +4382,33 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2210318</t>
+          <t>https://artportalen.se/Sighting/2210317</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2223673</v>
+        <v>2210318</v>
       </c>
       <c r="B32" t="n">
-        <v>111389</v>
+        <v>107608</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219711</v>
+        <v>219686</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4407,16 +4417,21 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hunderum, Öl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620063</v>
+        <v>620362</v>
       </c>
       <c r="R32" t="n">
-        <v>6352414</v>
+        <v>6352577</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4483,13 +4498,13 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2223673</t>
+          <t>https://artportalen.se/Sighting/2210318</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>64721316</v>
+        <v>2223673</v>
       </c>
       <c r="B33" t="n">
         <v>111389</v>
@@ -4518,19 +4533,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Enerums gamla bygata, Öl</t>
+          <t>Hunderum, Öl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620445</v>
+        <v>620063</v>
       </c>
       <c r="R33" t="n">
-        <v>6352579</v>
+        <v>6352414</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4557,12 +4569,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2012-04-21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2012-04-21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4576,18 +4588,18 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>lövängsrest</t>
+          <t>nyröjd betesmark med löv/barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Tommy Knutsson, Mikael Jeppson, Annika Sohlman</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4597,16 +4609,16 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64721316</t>
+          <t>https://artportalen.se/Sighting/2223673</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109482624</v>
+        <v>64721316</v>
       </c>
       <c r="B34" t="n">
-        <v>110078</v>
+        <v>111389</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4614,16 +4626,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220299</v>
+        <v>219711</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4635,20 +4647,19 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hunderum, Öl</t>
+          <t>Enerums gamla bygata, Öl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620373</v>
+        <v>620445</v>
       </c>
       <c r="R34" t="n">
-        <v>6352507</v>
+        <v>6352579</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4672,12 +4683,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2017-04-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-05-24</t>
+          <t>2017-04-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4686,34 +4697,42 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>lövängsrest</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mats Lindeborg</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Mats Lindeborg</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Tommy Knutsson, Mikael Jeppson, Annika Sohlman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109482624</t>
+          <t>https://artportalen.se/Sighting/64721316</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>64721431</v>
+        <v>109482624</v>
       </c>
       <c r="B35" t="n">
-        <v>110116</v>
+        <v>110078</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4721,16 +4740,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220320</v>
+        <v>220299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4740,25 +4759,22 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Enerums gamla bygata, Öl</t>
+          <t>Hunderum, Öl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620404</v>
+        <v>620373</v>
       </c>
       <c r="R35" t="n">
-        <v>6352538</v>
+        <v>6352507</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4782,12 +4798,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2023-05-24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4796,37 +4812,34 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Mats Lindeborg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Tommy Knutsson, Mikael Jeppson, Annika Sohlman</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Mats Lindeborg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64721431</t>
+          <t>https://artportalen.se/Sighting/109482624</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>99432761</v>
+        <v>64721431</v>
       </c>
       <c r="B36" t="n">
-        <v>110117</v>
+        <v>110116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4851,11 +4864,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
@@ -4863,20 +4872,19 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hunderum, Öl</t>
+          <t>Enerums gamla bygata, Öl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620373</v>
+        <v>620404</v>
       </c>
       <c r="R36" t="n">
-        <v>6352507</v>
+        <v>6352538</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4900,12 +4908,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-03-24</t>
+          <t>2017-04-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-03-24</t>
+          <t>2017-04-01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4914,51 +4922,54 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mats Lindeborg</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mats Lindeborg</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Tommy Knutsson, Mikael Jeppson, Annika Sohlman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99432761</t>
+          <t>https://artportalen.se/Sighting/64721431</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3511772</v>
+        <v>99432761</v>
       </c>
       <c r="B37" t="n">
-        <v>106812</v>
+        <v>110117</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220785</v>
+        <v>220320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4966,20 +4977,32 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hunderum, Öl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620172</v>
+        <v>620373</v>
       </c>
       <c r="R37" t="n">
-        <v>6352486</v>
+        <v>6352507</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5003,12 +5026,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2012-04-21</t>
+          <t>2022-03-24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2012-04-21</t>
+          <t>2022-03-24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5017,39 +5040,31 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>nyröjd betesmark med löv/barrskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Mats Lindeborg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Mats Lindeborg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3511772</t>
+          <t>https://artportalen.se/Sighting/99432761</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6792918</v>
+        <v>3511772</v>
       </c>
       <c r="B38" t="n">
         <v>106812</v>
@@ -5080,14 +5095,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hunderum VSV, Öl</t>
+          <t>Hunderum, Öl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>619723</v>
+        <v>620172</v>
       </c>
       <c r="R38" t="n">
-        <v>6352107</v>
+        <v>6352486</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5114,12 +5129,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2013-06-09</t>
+          <t>2012-04-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2013-06-09</t>
+          <t>2012-04-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5130,16 +5145,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>nyröjd betesmark med löv/barrskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Tommy Knutsson, Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -5149,16 +5169,16 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6792918</t>
+          <t>https://artportalen.se/Sighting/3511772</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>106118327</v>
+        <v>6792918</v>
       </c>
       <c r="B39" t="n">
-        <v>106813</v>
+        <v>106812</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5183,24 +5203,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hunderum, Öl</t>
+          <t>Hunderum VSV, Öl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620375</v>
+        <v>619723</v>
       </c>
       <c r="R39" t="n">
-        <v>6352520</v>
+        <v>6352107</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5222,19 +5238,14 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>0d78ed15-b49c-4bf3-a559-94eb6902c2cd</t>
-        </is>
-      </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
+          <t>2013-06-09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
+          <t>2013-06-09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5249,28 +5260,28 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Thomas Gunnarsson, Tommy Knutsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>Skyddsvärda träd</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106118327</t>
+          <t>https://artportalen.se/Sighting/6792918</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>106118329</v>
+        <v>106118327</v>
       </c>
       <c r="B40" t="n">
         <v>106813</v>
@@ -5309,10 +5320,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620231</v>
+        <v>620375</v>
       </c>
       <c r="R40" t="n">
-        <v>6352562</v>
+        <v>6352520</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5339,17 +5350,17 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>cf7c210a-0008-49c8-be8c-73e28e919daa</t>
+          <t>0d78ed15-b49c-4bf3-a559-94eb6902c2cd</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-03-24</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-03-24</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5379,13 +5390,13 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106118329</t>
+          <t>https://artportalen.se/Sighting/106118327</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>106118334</v>
+        <v>106118329</v>
       </c>
       <c r="B41" t="n">
         <v>106813</v>
@@ -5424,10 +5435,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620235</v>
+        <v>620231</v>
       </c>
       <c r="R41" t="n">
-        <v>6352560</v>
+        <v>6352562</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5454,7 +5465,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>d2a7f848-b73a-4baf-ba9b-7747ca18faae</t>
+          <t>cf7c210a-0008-49c8-be8c-73e28e919daa</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -5494,13 +5505,13 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106118334</t>
+          <t>https://artportalen.se/Sighting/106118329</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>106118335</v>
+        <v>106118334</v>
       </c>
       <c r="B42" t="n">
         <v>106813</v>
@@ -5539,10 +5550,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620230</v>
+        <v>620235</v>
       </c>
       <c r="R42" t="n">
-        <v>6352557</v>
+        <v>6352560</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5569,7 +5580,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>a472aba6-344e-41c8-96f4-e9c4884b67bb</t>
+          <t>d2a7f848-b73a-4baf-ba9b-7747ca18faae</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -5609,13 +5620,13 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106118335</t>
+          <t>https://artportalen.se/Sighting/106118334</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>106118336</v>
+        <v>106118335</v>
       </c>
       <c r="B43" t="n">
         <v>106813</v>
@@ -5654,10 +5665,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620278</v>
+        <v>620230</v>
       </c>
       <c r="R43" t="n">
-        <v>6352590</v>
+        <v>6352557</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5684,7 +5695,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>bc236d8d-60fc-4a51-a25e-619610e21894</t>
+          <t>a472aba6-344e-41c8-96f4-e9c4884b67bb</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -5724,13 +5735,13 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106118336</t>
+          <t>https://artportalen.se/Sighting/106118335</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>106118337</v>
+        <v>106118336</v>
       </c>
       <c r="B44" t="n">
         <v>106813</v>
@@ -5769,10 +5780,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620272</v>
+        <v>620278</v>
       </c>
       <c r="R44" t="n">
-        <v>6352599</v>
+        <v>6352590</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5799,7 +5810,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>a182c887-dc7f-40dd-84a0-e17f860b616d</t>
+          <t>bc236d8d-60fc-4a51-a25e-619610e21894</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -5839,13 +5850,13 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106118337</t>
+          <t>https://artportalen.se/Sighting/106118336</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>106118338</v>
+        <v>106118337</v>
       </c>
       <c r="B45" t="n">
         <v>106813</v>
@@ -5884,10 +5895,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620259</v>
+        <v>620272</v>
       </c>
       <c r="R45" t="n">
-        <v>6352637</v>
+        <v>6352599</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5914,7 +5925,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>103a7168-c4dd-462e-8ea1-4c740baab8d4</t>
+          <t>a182c887-dc7f-40dd-84a0-e17f860b616d</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -5925,11 +5936,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2022-03-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5959,13 +5965,13 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106118338</t>
+          <t>https://artportalen.se/Sighting/106118337</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>106120069</v>
+        <v>106118338</v>
       </c>
       <c r="B46" t="n">
         <v>106813</v>
@@ -6004,10 +6010,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620099</v>
+        <v>620259</v>
       </c>
       <c r="R46" t="n">
-        <v>6352422</v>
+        <v>6352637</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6034,17 +6040,22 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>7baf2393-be53-4742-ac18-f342238b554f</t>
+          <t>103a7168-c4dd-462e-8ea1-4c740baab8d4</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
+          <t>2022-03-24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
+          <t>2022-03-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6074,13 +6085,13 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106120069</t>
+          <t>https://artportalen.se/Sighting/106118338</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>106120070</v>
+        <v>106120069</v>
       </c>
       <c r="B47" t="n">
         <v>106813</v>
@@ -6119,10 +6130,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620089</v>
+        <v>620099</v>
       </c>
       <c r="R47" t="n">
-        <v>6352407</v>
+        <v>6352422</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6149,7 +6160,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>b3658e18-e98b-4416-8c35-e635f6a64c64</t>
+          <t>7baf2393-be53-4742-ac18-f342238b554f</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -6189,13 +6200,13 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106120070</t>
+          <t>https://artportalen.se/Sighting/106120069</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>106120071</v>
+        <v>106120070</v>
       </c>
       <c r="B48" t="n">
         <v>106813</v>
@@ -6234,10 +6245,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620117</v>
+        <v>620089</v>
       </c>
       <c r="R48" t="n">
-        <v>6352438</v>
+        <v>6352407</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6264,7 +6275,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>c395c2e6-2c2a-4da2-aea5-f610773a0889</t>
+          <t>b3658e18-e98b-4416-8c35-e635f6a64c64</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -6304,13 +6315,13 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106120071</t>
+          <t>https://artportalen.se/Sighting/106120070</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>106120072</v>
+        <v>106120071</v>
       </c>
       <c r="B49" t="n">
         <v>106813</v>
@@ -6349,10 +6360,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620186</v>
+        <v>620117</v>
       </c>
       <c r="R49" t="n">
-        <v>6352494</v>
+        <v>6352438</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6379,7 +6390,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>302c2685-e40a-4b24-9b45-1816889320c4</t>
+          <t>c395c2e6-2c2a-4da2-aea5-f610773a0889</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -6390,11 +6401,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2022-03-30</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>två hopväxta stammar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6424,33 +6430,33 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106120072</t>
+          <t>https://artportalen.se/Sighting/106120071</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3385010</v>
+        <v>106120072</v>
       </c>
       <c r="B50" t="n">
-        <v>106155</v>
+        <v>106813</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6458,20 +6464,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Enerums missionshus, Öl</t>
+          <t>Hunderum, Öl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620403</v>
+        <v>620186</v>
       </c>
       <c r="R50" t="n">
-        <v>6352691</v>
+        <v>6352494</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6493,14 +6503,24 @@
           <t>Böda</t>
         </is>
       </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>302c2685-e40a-4b24-9b45-1816889320c4</t>
+        </is>
+      </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2010-07-06</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2010-07-06</t>
+          <t>2022-03-30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>två hopväxta stammar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6511,37 +6531,32 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>vägkant</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Håkan Lundkvist</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Skyddsvärda träd</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3385010</t>
+          <t>https://artportalen.se/Sighting/106120072</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>6792891</v>
+        <v>3385010</v>
       </c>
       <c r="B51" t="n">
         <v>106155</v>
@@ -6572,14 +6587,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hunderum VSV, Öl</t>
+          <t>Enerums missionshus, Öl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>619723</v>
+        <v>620403</v>
       </c>
       <c r="R51" t="n">
-        <v>6352107</v>
+        <v>6352691</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6606,12 +6621,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2013-06-09</t>
+          <t>2010-07-06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2013-06-09</t>
+          <t>2010-07-06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6622,16 +6637,21 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Tommy Knutsson, Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson, Håkan Lundkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6641,16 +6661,16 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6792891</t>
+          <t>https://artportalen.se/Sighting/3385010</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>6792879</v>
+        <v>6792891</v>
       </c>
       <c r="B52" t="n">
-        <v>106328</v>
+        <v>106155</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6658,21 +6678,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221423</v>
+        <v>221141</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6747,13 +6767,13 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6792879</t>
+          <t>https://artportalen.se/Sighting/6792891</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>16178533</v>
+        <v>6792879</v>
       </c>
       <c r="B53" t="n">
         <v>106328</v>
@@ -6782,19 +6802,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hunderum SV-V, Öl</t>
+          <t>Hunderum VSV, Öl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>619726</v>
+        <v>619723</v>
       </c>
       <c r="R53" t="n">
-        <v>6352063</v>
+        <v>6352107</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6821,12 +6838,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2014-07-16</t>
+          <t>2013-06-09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2014-07-16</t>
+          <t>2013-06-09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6846,7 +6863,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Thomas Gunnarsson, Tommy Knutsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6856,16 +6873,16 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16178533</t>
+          <t>https://artportalen.se/Sighting/6792879</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>4958603</v>
+        <v>16178533</v>
       </c>
       <c r="B54" t="n">
-        <v>101325</v>
+        <v>106328</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6873,39 +6890,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>221423</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hunderum, Öl</t>
+          <t>Hunderum SV-V, Öl</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>619726</v>
       </c>
       <c r="R54" t="n">
-        <v>6352270</v>
+        <v>6352063</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6932,12 +6947,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2012-04-21</t>
+          <t>2014-07-16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2012-04-21</t>
+          <t>2014-07-16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6948,21 +6963,16 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>vägkant</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6972,13 +6982,13 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4958603</t>
+          <t>https://artportalen.se/Sighting/16178533</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4958604</v>
+        <v>4958603</v>
       </c>
       <c r="B55" t="n">
         <v>101325</v>
@@ -7018,10 +7028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620137</v>
+        <v>619726</v>
       </c>
       <c r="R55" t="n">
-        <v>6352391</v>
+        <v>6352270</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7067,7 +7077,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>nyröjd betesmark med löv/barrskog</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7088,13 +7098,13 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4958604</t>
+          <t>https://artportalen.se/Sighting/4958603</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>64721294</v>
+        <v>4958604</v>
       </c>
       <c r="B56" t="n">
         <v>101325</v>
@@ -7123,19 +7133,21 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Enerums gamla bygata, Öl</t>
+          <t>Hunderum, Öl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>620445</v>
+        <v>620137</v>
       </c>
       <c r="R56" t="n">
-        <v>6352579</v>
+        <v>6352391</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7162,12 +7174,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2012-04-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2012-04-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7178,16 +7190,21 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>nyröjd betesmark med löv/barrskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Tommy Knutsson, Mikael Jeppson, Annika Sohlman</t>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -7197,58 +7214,57 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64721294</t>
+          <t>https://artportalen.se/Sighting/4958604</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>106121020</v>
+        <v>64721294</v>
       </c>
       <c r="B57" t="n">
-        <v>103403</v>
+        <v>101325</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Hunderum, Öl</t>
+          <t>Enerums gamla bygata, Öl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>620424</v>
+        <v>620445</v>
       </c>
       <c r="R57" t="n">
-        <v>6352554</v>
+        <v>6352579</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7270,19 +7286,14 @@
           <t>Böda</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>01288943-353f-4f17-9d9a-33a75d81c7fd</t>
-        </is>
-      </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
+          <t>2017-04-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
+          <t>2017-04-01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7297,28 +7308,28 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Tommy Knutsson, Mikael Jeppson, Annika Sohlman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>Skyddsvärda träd</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106121020</t>
+          <t>https://artportalen.se/Sighting/64721294</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>106121021</v>
+        <v>106121020</v>
       </c>
       <c r="B58" t="n">
         <v>103403</v>
@@ -7357,10 +7368,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>620422</v>
+        <v>620424</v>
       </c>
       <c r="R58" t="n">
-        <v>6352556</v>
+        <v>6352554</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7387,7 +7398,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>66553441-8b62-408a-92a0-369b007fe058</t>
+          <t>01288943-353f-4f17-9d9a-33a75d81c7fd</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -7427,13 +7438,13 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106121021</t>
+          <t>https://artportalen.se/Sighting/106121020</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>106121022</v>
+        <v>106121021</v>
       </c>
       <c r="B59" t="n">
         <v>103403</v>
@@ -7472,10 +7483,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>620209</v>
+        <v>620422</v>
       </c>
       <c r="R59" t="n">
-        <v>6352522</v>
+        <v>6352556</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7502,7 +7513,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>023f81f6-0c24-47f3-8bcc-375e35b8dc5f</t>
+          <t>66553441-8b62-408a-92a0-369b007fe058</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -7542,13 +7553,13 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106121022</t>
+          <t>https://artportalen.se/Sighting/106121021</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>106121024</v>
+        <v>106121022</v>
       </c>
       <c r="B60" t="n">
         <v>103403</v>
@@ -7587,10 +7598,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>620363</v>
+        <v>620209</v>
       </c>
       <c r="R60" t="n">
-        <v>6352684</v>
+        <v>6352522</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7617,7 +7628,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>3997e162-6e76-4a9a-bae6-7bde92d81a8b</t>
+          <t>023f81f6-0c24-47f3-8bcc-375e35b8dc5f</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -7657,13 +7668,13 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106121024</t>
+          <t>https://artportalen.se/Sighting/106121022</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>106121025</v>
+        <v>106121024</v>
       </c>
       <c r="B61" t="n">
         <v>103403</v>
@@ -7702,10 +7713,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>620371</v>
+        <v>620363</v>
       </c>
       <c r="R61" t="n">
-        <v>6352712</v>
+        <v>6352684</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7732,7 +7743,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>6cd6412a-7278-4840-ab15-e695d71213c0</t>
+          <t>3997e162-6e76-4a9a-bae6-7bde92d81a8b</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -7772,54 +7783,58 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106121025</t>
+          <t>https://artportalen.se/Sighting/106121024</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>6526329</v>
+        <v>106121025</v>
       </c>
       <c r="B62" t="n">
-        <v>80992</v>
+        <v>103403</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>230185</v>
+        <v>223246</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hunderum, väst om byn, c 1km V. om bykorsningen. V. om Grytmon och S., Öl</t>
+          <t>Hunderum, Öl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>619643</v>
+        <v>620371</v>
       </c>
       <c r="R62" t="n">
-        <v>6352225</v>
+        <v>6352712</v>
       </c>
       <c r="S62" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7841,19 +7856,19 @@
           <t>Böda</t>
         </is>
       </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>6cd6412a-7278-4840-ab15-e695d71213c0</t>
+        </is>
+      </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>1999-09-16</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>1999-09-16</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Leg. Tommy Knutsson &amp; Håkan Lundkvist</t>
+          <t>2022-03-30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7864,29 +7879,140 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>På ek (Quercus) och klibbal (Alnus) i naturskogsartad blandskog med grov gran oc</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Thomas Johansson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106121025</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>6526329</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hunderum, väst om byn, c 1km V. om bykorsningen. V. om Grytmon och S., Öl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>619643</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6352225</v>
+      </c>
+      <c r="S63" t="n">
+        <v>100</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>1999-09-16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>1999-09-16</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Leg. Tommy Knutsson &amp; Håkan Lundkvist</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>På ek (Quercus) och klibbal (Alnus) i naturskogsartad blandskog med grov gran oc</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
           <t>Tommy Knutsson</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
+      <c r="AX63" t="inlineStr">
         <is>
           <t>Tommy Knutsson</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr">
+      <c r="AY63" t="inlineStr">
         <is>
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
+      <c r="AZ63" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6526329</t>
         </is>
@@ -7955,6 +8081,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2739-2022 artfynd.xlsx
+++ b/artfynd/S 2739-2022 artfynd.xlsx
@@ -3501,7 +3501,7 @@
         <v>137255053</v>
       </c>
       <c r="B25" t="n">
-        <v>9418</v>
+        <v>9424</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
